--- a/main/ig/ValueSet-type-systeme-information-vs.xlsx
+++ b/main/ig/ValueSet-type-systeme-information-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T09:04:56+00:00</t>
+    <t>2024-02-19T13:34:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-type-systeme-information-vs.xlsx
+++ b/main/ig/ValueSet-type-systeme-information-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:34:28+00:00</t>
+    <t>2024-02-19T13:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-type-systeme-information-vs.xlsx
+++ b/main/ig/ValueSet-type-systeme-information-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:42:29+00:00</t>
+    <t>2024-03-04T16:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-type-systeme-information-vs.xlsx
+++ b/main/ig/ValueSet-type-systeme-information-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-04T16:55:03+00:00</t>
+    <t>2024-03-05T15:34:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-type-systeme-information-vs.xlsx
+++ b/main/ig/ValueSet-type-systeme-information-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-05T15:34:40+00:00</t>
+    <t>2024-03-06T10:45:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
